--- a/tescase api.xlsx
+++ b/tescase api.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\belajarqa\test\petswager_api\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\belajarqa\test\api-petswager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C31C83-0FE3-43F4-BEBD-ECE0FC114EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2A6FC2-B1B9-407E-9BAE-E43F82EB4849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BF5AAC14-941B-4492-A128-674180ACF797}"/>
   </bookViews>
@@ -257,10 +257,6 @@
     <t xml:space="preserve">Status code 404 not found </t>
   </si>
   <si>
-    <t>Statu  code 404 massage
-not found</t>
-  </si>
-  <si>
     <t>TS.User_08</t>
   </si>
   <si>
@@ -962,6 +958,11 @@
   </si>
   <si>
     <t>Documenter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status code 404 not found
+respon body  code 1 message not found
+ </t>
   </si>
 </sst>
 </file>
@@ -1562,7 +1563,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1631,10 +1632,10 @@
         <v>6</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>7</v>
@@ -1643,7 +1644,7 @@
         <v>8</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>9</v>
@@ -1664,7 +1665,7 @@
         <v>14</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="170.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1684,13 +1685,13 @@
         <v>18</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>19</v>
@@ -1699,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>20</v>
@@ -1728,10 +1729,10 @@
         <v>27</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>28</v>
@@ -1758,10 +1759,10 @@
         <v>30</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R7" s="5"/>
     </row>
@@ -1782,10 +1783,10 @@
         <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>40</v>
@@ -1826,13 +1827,13 @@
         <v>15</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>58</v>
@@ -1864,22 +1865,22 @@
         <v>45</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>19</v>
@@ -1888,10 +1889,10 @@
         <v>1</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>47</v>
@@ -1903,10 +1904,10 @@
         <v>51</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
@@ -1917,7 +1918,7 @@
         <v>53</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>15</v>
@@ -1926,10 +1927,10 @@
         <v>61</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>57</v>
@@ -1941,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>59</v>
@@ -1953,7 +1954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>54</v>
       </c>
@@ -1970,10 +1971,10 @@
         <v>63</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>64</v>
@@ -1985,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>261</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>22</v>
@@ -1999,10 +2000,10 @@
     </row>
     <row r="13" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>62</v>
@@ -2011,16 +2012,16 @@
         <v>26</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>19</v>
@@ -2029,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="M13" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="N13" s="8" t="s">
         <v>22</v>
@@ -2043,25 +2044,25 @@
     </row>
     <row r="14" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>64</v>
@@ -2073,13 +2074,13 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N14" s="8" t="s">
         <v>22</v>
@@ -2087,25 +2088,25 @@
     </row>
     <row r="15" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="5" t="s">
@@ -2115,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L15" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>29</v>
@@ -2130,36 +2131,36 @@
         <v>51</v>
       </c>
       <c r="P15" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q15" s="14" t="s">
         <v>230</v>
-      </c>
-      <c r="Q15" s="14" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>19</v>
@@ -2168,13 +2169,13 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="M16" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="N16" s="8" t="s">
         <v>22</v>
@@ -2182,28 +2183,28 @@
     </row>
     <row r="17" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>107</v>
-      </c>
       <c r="C17" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" s="6" t="s">
+      <c r="H17" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>19</v>
@@ -2212,7 +2213,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>65</v>
@@ -2226,7 +2227,7 @@
     </row>
     <row r="18" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B18" s="24"/>
       <c r="C18" s="24"/>
@@ -2247,28 +2248,28 @@
     </row>
     <row r="19" spans="1:18" ht="232" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="H19" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>19</v>
@@ -2277,13 +2278,13 @@
         <v>1</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N19" s="8" t="s">
         <v>22</v>
@@ -2291,25 +2292,25 @@
     </row>
     <row r="20" spans="1:18" ht="243.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="C20" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>19</v>
@@ -2318,13 +2319,13 @@
         <v>1</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>31</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N20" s="8" t="s">
         <v>22</v>
@@ -2333,36 +2334,36 @@
         <v>30</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q20" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>19</v>
@@ -2371,13 +2372,13 @@
         <v>1</v>
       </c>
       <c r="K21" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="M21" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="N21" s="8" t="s">
         <v>22</v>
@@ -2385,28 +2386,28 @@
     </row>
     <row r="22" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>145</v>
-      </c>
       <c r="C22" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="G22" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>19</v>
@@ -2415,13 +2416,13 @@
         <v>1</v>
       </c>
       <c r="K22" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L22" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="L22" s="6" t="s">
-        <v>150</v>
-      </c>
       <c r="M22" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N22" s="8" t="s">
         <v>22</v>
@@ -2429,28 +2430,28 @@
     </row>
     <row r="23" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>153</v>
-      </c>
       <c r="C23" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>19</v>
@@ -2459,13 +2460,13 @@
         <v>1</v>
       </c>
       <c r="K23" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="L23" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="M23" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N23" s="8" t="s">
         <v>22</v>
@@ -2473,28 +2474,28 @@
     </row>
     <row r="24" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="C24" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>19</v>
@@ -2503,13 +2504,13 @@
         <v>1</v>
       </c>
       <c r="K24" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>166</v>
-      </c>
       <c r="M24" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N24" s="8" t="s">
         <v>50</v>
@@ -2518,36 +2519,36 @@
         <v>30</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q24" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="G25" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>19</v>
@@ -2556,13 +2557,13 @@
         <v>1</v>
       </c>
       <c r="K25" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="L25" s="4" t="s">
+      <c r="M25" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="M25" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="N25" s="8" t="s">
         <v>22</v>
@@ -2570,28 +2571,28 @@
     </row>
     <row r="26" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>19</v>
@@ -2600,13 +2601,13 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N26" s="8" t="s">
         <v>22</v>
@@ -2614,7 +2615,7 @@
     </row>
     <row r="27" spans="1:18" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -2635,25 +2636,25 @@
     </row>
     <row r="28" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="F28" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="G28" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>40</v>
@@ -2665,13 +2666,13 @@
         <v>1</v>
       </c>
       <c r="K28" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="L28" s="6" t="s">
-        <v>192</v>
-      </c>
       <c r="M28" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N28" s="8" t="s">
         <v>22</v>
@@ -2679,28 +2680,28 @@
     </row>
     <row r="29" spans="1:18" ht="127.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>186</v>
-      </c>
       <c r="C29" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="G29" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>198</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>19</v>
@@ -2709,13 +2710,13 @@
         <v>1</v>
       </c>
       <c r="K29" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="L29" s="6" t="s">
-        <v>200</v>
-      </c>
       <c r="M29" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N29" s="8" t="s">
         <v>22</v>
@@ -2723,28 +2724,28 @@
     </row>
     <row r="30" spans="1:18" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="F30" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>204</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>205</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>19</v>
@@ -2753,13 +2754,13 @@
         <v>1</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N30" s="8" t="s">
         <v>50</v>
@@ -2768,37 +2769,37 @@
         <v>51</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q30" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="R30" s="5"/>
     </row>
     <row r="31" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>209</v>
-      </c>
       <c r="F31" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>19</v>
@@ -2807,13 +2808,13 @@
         <v>1</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N31" s="8" t="s">
         <v>22</v>
@@ -2821,28 +2822,28 @@
     </row>
     <row r="32" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>19</v>
@@ -2851,13 +2852,13 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L32" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="M32" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="N32" s="8" t="s">
         <v>22</v>
@@ -2865,28 +2866,28 @@
     </row>
     <row r="33" spans="1:17" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>19</v>
@@ -2895,13 +2896,13 @@
         <v>1</v>
       </c>
       <c r="K33" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="M33" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="N33" s="8" t="s">
         <v>50</v>
@@ -2910,36 +2911,36 @@
         <v>30</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>240</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>19</v>
@@ -2948,13 +2949,13 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="L34" s="6" t="s">
-        <v>244</v>
-      </c>
       <c r="M34" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N34" s="8" t="s">
         <v>22</v>
@@ -2962,28 +2963,28 @@
     </row>
     <row r="35" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>19</v>
@@ -2992,13 +2993,13 @@
         <v>1</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N35" s="8" t="s">
         <v>22</v>
@@ -3006,28 +3007,28 @@
     </row>
     <row r="36" spans="1:17" ht="87" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>250</v>
-      </c>
       <c r="C36" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>253</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>19</v>
@@ -3036,13 +3037,13 @@
         <v>1</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N36" s="8" t="s">
         <v>29</v>
@@ -3051,10 +3052,10 @@
         <v>30</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/tescase api.xlsx
+++ b/tescase api.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\belajarqa\test\api-petswager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2A6FC2-B1B9-407E-9BAE-E43F82EB4849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF336DC-2B42-44C5-B58F-8D5B590EBD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BF5AAC14-941B-4492-A128-674180ACF797}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="263">
   <si>
     <t>Name Tester: Dimas Akbar Maulana</t>
   </si>
@@ -963,6 +963,9 @@
     <t xml:space="preserve">Status code 404 not found
 respon body  code 1 message not found
  </t>
+  </si>
+  <si>
+    <t>v2/user/dimas1</t>
   </si>
 </sst>
 </file>
@@ -2103,7 +2106,7 @@
         <v>82</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>101</v>
+        <v>262</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>111</v>

--- a/tescase api.xlsx
+++ b/tescase api.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\belajarqa\test\api-petswager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF336DC-2B42-44C5-B58F-8D5B590EBD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC39D57-CCA1-4E15-8FD0-DA63714B5E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BF5AAC14-941B-4492-A128-674180ACF797}"/>
   </bookViews>
@@ -417,9 +417,6 @@
     <t>PUT</t>
   </si>
   <si>
-    <t>Username = dimasa1</t>
-  </si>
-  <si>
     <t>Request path 
 paramater Delete/user</t>
   </si>
@@ -966,6 +963,9 @@
   </si>
   <si>
     <t>v2/user/dimas1</t>
+  </si>
+  <si>
+    <t>Username = dimas1</t>
   </si>
 </sst>
 </file>
@@ -1566,7 +1566,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1668,7 +1668,7 @@
         <v>14</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="170.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1762,10 +1762,10 @@
         <v>30</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R7" s="5"/>
     </row>
@@ -1907,10 +1907,10 @@
         <v>51</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
@@ -1992,10 +1992,10 @@
         <v>72</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>22</v>
@@ -2106,7 +2106,7 @@
         <v>82</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>111</v>
@@ -2134,10 +2134,10 @@
         <v>51</v>
       </c>
       <c r="P15" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q15" s="14" t="s">
         <v>229</v>
-      </c>
-      <c r="Q15" s="14" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
@@ -2160,10 +2160,10 @@
         <v>101</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>112</v>
+        <v>262</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>19</v>
@@ -2172,13 +2172,13 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="M16" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="N16" s="8" t="s">
         <v>22</v>
@@ -2192,22 +2192,22 @@
         <v>106</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="E17" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>101</v>
       </c>
       <c r="G17" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>19</v>
@@ -2216,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>65</v>
@@ -2230,7 +2230,7 @@
     </row>
     <row r="18" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B18" s="24"/>
       <c r="C18" s="24"/>
@@ -2251,28 +2251,28 @@
     </row>
     <row r="19" spans="1:18" ht="232" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="H19" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>19</v>
@@ -2284,10 +2284,10 @@
         <v>87</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N19" s="8" t="s">
         <v>22</v>
@@ -2295,25 +2295,25 @@
     </row>
     <row r="20" spans="1:18" ht="243.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="C20" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>19</v>
@@ -2322,13 +2322,13 @@
         <v>1</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>31</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N20" s="8" t="s">
         <v>22</v>
@@ -2337,36 +2337,36 @@
         <v>30</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q20" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>110</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>19</v>
@@ -2375,13 +2375,13 @@
         <v>1</v>
       </c>
       <c r="K21" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="M21" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>142</v>
       </c>
       <c r="N21" s="8" t="s">
         <v>22</v>
@@ -2389,28 +2389,28 @@
     </row>
     <row r="22" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>144</v>
-      </c>
       <c r="C22" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>110</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>19</v>
@@ -2419,13 +2419,13 @@
         <v>1</v>
       </c>
       <c r="K22" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="L22" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="L22" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="M22" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N22" s="8" t="s">
         <v>22</v>
@@ -2433,28 +2433,28 @@
     </row>
     <row r="23" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>152</v>
-      </c>
       <c r="C23" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>111</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>19</v>
@@ -2463,13 +2463,13 @@
         <v>1</v>
       </c>
       <c r="K23" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="L23" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>159</v>
-      </c>
       <c r="M23" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N23" s="8" t="s">
         <v>22</v>
@@ -2477,28 +2477,28 @@
     </row>
     <row r="24" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>161</v>
-      </c>
       <c r="C24" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>111</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>19</v>
@@ -2507,13 +2507,13 @@
         <v>1</v>
       </c>
       <c r="K24" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>165</v>
-      </c>
       <c r="M24" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N24" s="8" t="s">
         <v>50</v>
@@ -2522,36 +2522,36 @@
         <v>30</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q24" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="G25" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>171</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>19</v>
@@ -2560,13 +2560,13 @@
         <v>1</v>
       </c>
       <c r="K25" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L25" s="4" t="s">
+      <c r="M25" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="M25" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="N25" s="8" t="s">
         <v>22</v>
@@ -2574,28 +2574,28 @@
     </row>
     <row r="26" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>19</v>
@@ -2604,13 +2604,13 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N26" s="8" t="s">
         <v>22</v>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="27" spans="1:18" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="28" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="F28" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>110</v>
@@ -2669,13 +2669,13 @@
         <v>1</v>
       </c>
       <c r="K28" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="L28" s="6" t="s">
-        <v>191</v>
-      </c>
       <c r="M28" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N28" s="8" t="s">
         <v>22</v>
@@ -2683,28 +2683,28 @@
     </row>
     <row r="29" spans="1:18" ht="127.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>185</v>
-      </c>
       <c r="C29" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="G29" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>19</v>
@@ -2713,13 +2713,13 @@
         <v>1</v>
       </c>
       <c r="K29" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="L29" s="6" t="s">
-        <v>199</v>
-      </c>
       <c r="M29" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N29" s="8" t="s">
         <v>22</v>
@@ -2727,28 +2727,28 @@
     </row>
     <row r="30" spans="1:18" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="F30" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>204</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>19</v>
@@ -2757,13 +2757,13 @@
         <v>1</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N30" s="8" t="s">
         <v>50</v>
@@ -2772,37 +2772,37 @@
         <v>51</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q30" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R30" s="5"/>
     </row>
     <row r="31" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>208</v>
-      </c>
       <c r="F31" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>19</v>
@@ -2811,13 +2811,13 @@
         <v>1</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N31" s="8" t="s">
         <v>22</v>
@@ -2825,28 +2825,28 @@
     </row>
     <row r="32" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>215</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>110</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>19</v>
@@ -2855,13 +2855,13 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L32" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="M32" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>217</v>
       </c>
       <c r="N32" s="8" t="s">
         <v>22</v>
@@ -2869,28 +2869,28 @@
     </row>
     <row r="33" spans="1:17" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>110</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>19</v>
@@ -2899,13 +2899,13 @@
         <v>1</v>
       </c>
       <c r="K33" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="M33" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="N33" s="8" t="s">
         <v>50</v>
@@ -2914,36 +2914,36 @@
         <v>30</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>238</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>239</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>19</v>
@@ -2952,13 +2952,13 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="L34" s="6" t="s">
-        <v>243</v>
-      </c>
       <c r="M34" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N34" s="8" t="s">
         <v>22</v>
@@ -2966,28 +2966,28 @@
     </row>
     <row r="35" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>247</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>19</v>
@@ -2996,13 +2996,13 @@
         <v>1</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N35" s="8" t="s">
         <v>22</v>
@@ -3010,28 +3010,28 @@
     </row>
     <row r="36" spans="1:17" ht="87" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>249</v>
-      </c>
       <c r="C36" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>251</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>252</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>19</v>
@@ -3040,13 +3040,13 @@
         <v>1</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N36" s="8" t="s">
         <v>29</v>
@@ -3055,10 +3055,10 @@
         <v>30</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/tescase api.xlsx
+++ b/tescase api.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\belajarqa\test\api-petswager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC39D57-CCA1-4E15-8FD0-DA63714B5E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE2BBFC-C9DB-44EE-9A23-55752119B075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BF5AAC14-941B-4492-A128-674180ACF797}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="266">
   <si>
     <t>Name Tester: Dimas Akbar Maulana</t>
   </si>
@@ -477,24 +477,6 @@
   </si>
   <si>
     <t xml:space="preserve">Validasi pet product </t>
-  </si>
-  <si>
-    <t>{
-    "id": 0,
-    "kategori":{
-        "id": 0,
-        "nama":"peliharaan "
-    },
-    "name":"persia ",
-    "photourl":[
-        "kucing.jpg"
-    ],
-    "tags":[{
-        "id": 0,
-        "name": "persia"
-    }],
-    "status":"availabel"
-}</t>
   </si>
   <si>
     <t>{
@@ -966,6 +948,33 @@
   </si>
   <si>
     <t>Username = dimas1</t>
+  </si>
+  <si>
+    <t>{
+    "id": 1,
+    "kategori":{
+        "id": 0,
+        "nama":"peliharaan "
+    },
+    "name":"persia ",
+    "photourl":[
+        "kucing.jpg"
+    ],
+    "tags":[{
+        "id": 0,
+        "name": "persia"
+    }],
+    "status":"availabel"
+}</t>
+  </si>
+  <si>
+    <t>Check id yang tidak ada dalam data base</t>
+  </si>
+  <si>
+    <t>ID = 2000</t>
+  </si>
+  <si>
+    <t>Kirim request get dengan id 2000</t>
   </si>
 </sst>
 </file>
@@ -1544,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE44FA60-05FE-4DBC-B511-5D2F9E0B5700}">
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -1566,7 +1575,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1668,7 +1677,7 @@
         <v>14</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="170.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1762,10 +1771,10 @@
         <v>30</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R7" s="5"/>
     </row>
@@ -1907,10 +1916,10 @@
         <v>51</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
@@ -1992,10 +2001,10 @@
         <v>72</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>22</v>
@@ -2106,7 +2115,7 @@
         <v>82</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>111</v>
@@ -2134,10 +2143,10 @@
         <v>51</v>
       </c>
       <c r="P15" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q15" s="14" t="s">
         <v>228</v>
-      </c>
-      <c r="Q15" s="14" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
@@ -2163,7 +2172,7 @@
         <v>117</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>19</v>
@@ -2254,7 +2263,7 @@
         <v>121</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>124</v>
@@ -2272,7 +2281,7 @@
         <v>127</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>19</v>
@@ -2307,13 +2316,13 @@
         <v>26</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>126</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>19</v>
@@ -2322,13 +2331,13 @@
         <v>1</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>31</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N20" s="8" t="s">
         <v>22</v>
@@ -2337,27 +2346,27 @@
         <v>30</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q20" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>129</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>126</v>
@@ -2366,7 +2375,7 @@
         <v>110</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>19</v>
@@ -2375,42 +2384,42 @@
         <v>1</v>
       </c>
       <c r="K21" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="M21" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="N21" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="C22" s="5" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>144</v>
+        <v>263</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>110</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>146</v>
+        <v>264</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>19</v>
@@ -2418,43 +2427,43 @@
       <c r="J22" s="8">
         <v>1</v>
       </c>
-      <c r="K22" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>148</v>
+      <c r="K22" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="N22" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>153</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>156</v>
+        <v>110</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>19</v>
@@ -2462,34 +2471,34 @@
       <c r="J23" s="8">
         <v>1</v>
       </c>
-      <c r="K23" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>158</v>
+      <c r="K23" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="N23" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>126</v>
@@ -2497,8 +2506,8 @@
       <c r="G24" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>162</v>
+      <c r="H24" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>19</v>
@@ -2507,51 +2516,42 @@
         <v>1</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="M24" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="N24" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q24" s="16" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
-        <v>165</v>
-      </c>
       <c r="B25" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>19</v>
@@ -2560,42 +2560,51 @@
         <v>1</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>172</v>
+        <v>162</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q25" s="16" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>177</v>
+        <v>15</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>117</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>19</v>
@@ -2604,107 +2613,107 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="L26" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="L26" s="6" t="s">
-        <v>180</v>
-      </c>
       <c r="M26" s="6" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N26" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="25" t="s">
+    <row r="27" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="8">
+        <v>1</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+    </row>
+    <row r="29" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-    </row>
-    <row r="28" spans="1:18" ht="58" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B29" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E29" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="G29" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H29" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" s="8">
-        <v>1</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="127.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>19</v>
@@ -2713,42 +2722,42 @@
         <v>1</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="N29" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="127.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>201</v>
-      </c>
       <c r="D30" s="5" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>127</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>19</v>
@@ -2757,52 +2766,42 @@
         <v>1</v>
       </c>
       <c r="K30" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="L30" s="6" t="s">
-        <v>208</v>
-      </c>
       <c r="M30" s="6" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="N30" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q30" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="R30" s="5"/>
-    </row>
-    <row r="31" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>207</v>
-      </c>
       <c r="F31" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>127</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>19</v>
@@ -2811,42 +2810,52 @@
         <v>1</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L31" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q31" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="R31" s="5"/>
+    </row>
+    <row r="32" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="M31" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>19</v>
@@ -2855,42 +2864,42 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="N32" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C33" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>221</v>
-      </c>
       <c r="F33" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>110</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>222</v>
+        <v>169</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>19</v>
@@ -2899,51 +2908,42 @@
         <v>1</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="O33" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="P33" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q33" s="12" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>19</v>
@@ -2952,42 +2952,51 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="N34" s="8" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q34" s="12" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>177</v>
+        <v>15</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>117</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>19</v>
@@ -2996,42 +3005,42 @@
         <v>1</v>
       </c>
       <c r="K35" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="L35" s="6" t="s">
-        <v>224</v>
-      </c>
       <c r="M35" s="6" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="N35" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="87" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>250</v>
-      </c>
       <c r="F36" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="H36" s="5" t="s">
-        <v>251</v>
+      <c r="H36" s="6" t="s">
+        <v>245</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>19</v>
@@ -3040,25 +3049,69 @@
         <v>1</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="M36" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="N36" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="87" x14ac:dyDescent="0.35">
+      <c r="A37" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" s="8">
+        <v>1</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q37" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="N36" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O36" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="P36" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q36" s="12" t="s">
-        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -3067,7 +3120,7 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:Q4"/>
     <mergeCell ref="A18:Q18"/>
-    <mergeCell ref="A27:Q27"/>
+    <mergeCell ref="A28:Q28"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
@@ -3078,10 +3131,10 @@
     <hyperlink ref="Q10" r:id="rId5" xr:uid="{A53B9D08-AEB5-4E38-966F-550BCDA2D889}"/>
     <hyperlink ref="Q15" r:id="rId6" xr:uid="{70C848DD-AF51-48AF-9E54-93A495C9F879}"/>
     <hyperlink ref="Q20" r:id="rId7" xr:uid="{BC229182-103D-4981-BA54-A17DE82333C1}"/>
-    <hyperlink ref="Q24" r:id="rId8" xr:uid="{BA5BFB44-A21D-4BC6-A11B-A7CADA5D0EDF}"/>
-    <hyperlink ref="Q30" r:id="rId9" xr:uid="{A4CD73CD-94FF-4E59-9692-2B171434C6F4}"/>
-    <hyperlink ref="Q33" r:id="rId10" xr:uid="{BB5336E2-44F3-464A-B18E-295B31DEC8BC}"/>
-    <hyperlink ref="Q36" r:id="rId11" xr:uid="{4CC3B898-1847-49CB-87C6-7CB68BA86153}"/>
+    <hyperlink ref="Q25" r:id="rId8" xr:uid="{BA5BFB44-A21D-4BC6-A11B-A7CADA5D0EDF}"/>
+    <hyperlink ref="Q31" r:id="rId9" xr:uid="{A4CD73CD-94FF-4E59-9692-2B171434C6F4}"/>
+    <hyperlink ref="Q34" r:id="rId10" xr:uid="{BB5336E2-44F3-464A-B18E-295B31DEC8BC}"/>
+    <hyperlink ref="Q37" r:id="rId11" xr:uid="{4CC3B898-1847-49CB-87C6-7CB68BA86153}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tescase api.xlsx
+++ b/tescase api.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\belajarqa\test\api-petswager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE2BBFC-C9DB-44EE-9A23-55752119B075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA3C7FE-5D7D-4FD5-82E3-B3001C47AFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BF5AAC14-941B-4492-A128-674180ACF797}"/>
   </bookViews>
@@ -885,9 +885,6 @@
     <t>TC.Store_09</t>
   </si>
   <si>
-    <t xml:space="preserve">Melakukan validasi 405 delete order by id </t>
-  </si>
-  <si>
     <t xml:space="preserve">Melakukan validasi 400 delete order by id </t>
   </si>
   <si>
@@ -926,14 +923,6 @@
     <t xml:space="preserve">
 Pada gambar 6
  terjadi kesalahan validasi server erro saat quantity produk terlalu banyak </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Pada gambar 7 terjadi kesalahan validasi  yang seharusnya 400 menajadi 405 not found </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Pada gambar 8 terjadi kesalahan validasi  yang seharusnya 400 menajadi 405 not found</t>
   </si>
   <si>
     <t>Documenter</t>
@@ -975,6 +964,17 @@
   </si>
   <si>
     <t>Kirim request get dengan id 2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Pada gambar 7 terjadi kesalahan validasi  yang seharusnya 400 menajadi 404 not found </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Pada gambar 8 terjadi kesalahan validasi  yang seharusnya 400 menajadi 404 not found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melakukan validasi 404 delete order by id </t>
   </si>
 </sst>
 </file>
@@ -1677,7 +1677,7 @@
         <v>14</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="170.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2001,10 +2001,10 @@
         <v>72</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>22</v>
@@ -2115,7 +2115,7 @@
         <v>82</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>111</v>
@@ -2172,7 +2172,7 @@
         <v>117</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>19</v>
@@ -2281,7 +2281,7 @@
         <v>127</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>19</v>
@@ -2346,7 +2346,7 @@
         <v>30</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q20" s="16" t="s">
         <v>229</v>
@@ -2410,7 +2410,7 @@
         <v>26</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>126</v>
@@ -2419,7 +2419,7 @@
         <v>110</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>19</v>
@@ -2428,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="L22" s="4" t="s">
         <v>65</v>
@@ -2575,7 +2575,7 @@
         <v>30</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q25" s="16" t="s">
         <v>231</v>
@@ -2825,7 +2825,7 @@
         <v>51</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q31" s="11" t="s">
         <v>230</v>
@@ -2967,7 +2967,7 @@
         <v>30</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="Q34" s="12" t="s">
         <v>234</v>
@@ -3031,7 +3031,7 @@
         <v>176</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>194</v>
@@ -3075,7 +3075,7 @@
         <v>176</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>194</v>
@@ -3084,7 +3084,7 @@
         <v>117</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>19</v>
@@ -3099,7 +3099,7 @@
         <v>208</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N37" s="8" t="s">
         <v>29</v>
@@ -3108,10 +3108,10 @@
         <v>30</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="Q37" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
